--- a/DATA/分岐器半径計算表.xlsx
+++ b/DATA/分岐器半径計算表.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520"/>
@@ -11,7 +11,7 @@
     <sheet name="摩擦係数" sheetId="10" r:id="rId2"/>
     <sheet name="Excel方眼" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -659,7 +659,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4722,11 +4722,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="227019008"/>
-        <c:axId val="227033088"/>
+        <c:axId val="192327616"/>
+        <c:axId val="192328192"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="227019008"/>
+        <c:axId val="192327616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4783,12 +4783,12 @@
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="227033088"/>
+        <c:crossAx val="192328192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="227033088"/>
+        <c:axId val="192328192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4845,7 +4845,7 @@
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="227019008"/>
+        <c:crossAx val="192327616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -8099,7 +8099,7 @@
         <v>26</v>
       </c>
       <c r="O46">
-        <v>530</v>
+        <v>800</v>
       </c>
       <c r="P46" t="s">
         <v>32</v>
@@ -8108,7 +8108,7 @@
         <v>26</v>
       </c>
       <c r="U46">
-        <v>820</v>
+        <v>580</v>
       </c>
       <c r="V46" t="s">
         <v>32</v>
@@ -8119,7 +8119,7 @@
         <v>25</v>
       </c>
       <c r="O47">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="P47" t="s">
         <v>33</v>
@@ -8128,7 +8128,7 @@
         <v>40</v>
       </c>
       <c r="U47">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="V47" t="s">
         <v>34</v>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="U52">
         <f>3.5*SQRT(U46)</f>
-        <v>100.22474744293447</v>
+        <v>84.291162051546067</v>
       </c>
     </row>
     <row r="53" spans="14:22" x14ac:dyDescent="0.4">
@@ -8202,7 +8202,7 @@
         <v>27</v>
       </c>
       <c r="O53">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="P53" t="s">
         <v>34</v>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="U53">
         <f>SQRT(U46*(U47+U49)/8.4)</f>
-        <v>108.2325538564332</v>
+        <v>92.902919119650804</v>
       </c>
     </row>
     <row r="54" spans="14:22" x14ac:dyDescent="0.4">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="O54">
         <f>3.5*SQRT(O46)</f>
-        <v>80.576051032549358</v>
+        <v>98.994949366116657</v>
       </c>
       <c r="P54" t="s">
         <v>33</v>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="O57">
         <f>0.4*O53</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="P57" t="s">
         <v>32</v>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O58">
         <f>0.01*O53*O47</f>
-        <v>18</v>
+        <v>52.250000000000007</v>
       </c>
       <c r="P58" t="s">
         <v>32</v>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O59">
         <f>0.009*O49*O47</f>
-        <v>28.35</v>
+        <v>59.85</v>
       </c>
       <c r="P59" t="s">
         <v>32</v>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O60">
         <f>MAX(O57:O59)</f>
-        <v>28.35</v>
+        <v>59.85</v>
       </c>
       <c r="P60" t="s">
         <v>32</v>
@@ -11078,7 +11078,8 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
